--- a/Template_insertion_adherents.xlsx
+++ b/Template_insertion_adherents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\sebtp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B355B0-C0A5-4EDB-8821-88B8CDE551CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5C1B65-582F-4359-AA3B-9E47EA5615BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
   </bookViews>
@@ -156,15 +156,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -172,14 +178,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -495,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431D5AF4-6942-4C44-8FEC-F31AB43C3EB5}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -524,128 +547,209 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <v>1</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="W2" s="3"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Template_insertion_adherents.xlsx
+++ b/Template_insertion_adherents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\sebtp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5C1B65-582F-4359-AA3B-9E47EA5615BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2E5A35-7CC9-40C4-B633-AF0FE5C0BCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
+    <workbookView xWindow="5412" yWindow="1644" windowWidth="17280" windowHeight="8880" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>email</t>
   </si>
@@ -87,52 +87,25 @@
     <t>fichiers</t>
   </si>
   <si>
-    <t>Ampatsakana</t>
+    <t>otigroupe.com</t>
+  </si>
+  <si>
+    <t>cot_fmfp (Oui/Non)</t>
+  </si>
+  <si>
+    <t>statut membre (Simple/Bureau)</t>
+  </si>
+  <si>
+    <t>statut (radie, actif, inactif, demande)</t>
+  </si>
+  <si>
+    <t>actif</t>
   </si>
   <si>
     <t>OTI</t>
   </si>
   <si>
-    <t>otigroupe.com</t>
-  </si>
-  <si>
-    <t>BTP</t>
-  </si>
-  <si>
-    <t>oui</t>
-  </si>
-  <si>
-    <t>cot_fmfp (Oui/Non)</t>
-  </si>
-  <si>
-    <t>Hary</t>
-  </si>
-  <si>
-    <t>exemple</t>
-  </si>
-  <si>
-    <t>oti@oti.mg</t>
-  </si>
-  <si>
-    <t>038 00 304 40</t>
-  </si>
-  <si>
-    <t>Simple</t>
-  </si>
-  <si>
-    <t>statut membre (Simple/Bureau)</t>
-  </si>
-  <si>
-    <t>2 ans</t>
-  </si>
-  <si>
-    <t>statut (radie, actif, inactif, demande)</t>
-  </si>
-  <si>
-    <t>actif</t>
-  </si>
-  <si>
-    <t>Entreprise</t>
+    <t>secoti@oti.mg</t>
   </si>
 </sst>
 </file>
@@ -572,7 +545,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -584,7 +557,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -593,7 +566,7 @@
         <v>12</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>13</v>
@@ -619,61 +592,35 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
-      <c r="V2" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="V2" s="3"/>
       <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -753,7 +700,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{717D8415-1D27-462C-AE74-5A0E936625B3}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{9A0FD041-1250-4C6A-9B1B-06B7A10EAE0D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Template_insertion_adherents.xlsx
+++ b/Template_insertion_adherents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\sebtp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2E5A35-7CC9-40C4-B633-AF0FE5C0BCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7801F72A-014A-4F27-9215-5A25AE307D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5412" yWindow="1644" windowWidth="17280" windowHeight="8880" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
+    <workbookView xWindow="5760" yWindow="1992" windowWidth="17280" windowHeight="8880" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>email</t>
   </si>
@@ -106,6 +106,21 @@
   </si>
   <si>
     <t>secoti@oti.mg</t>
+  </si>
+  <si>
+    <t>NIF</t>
+  </si>
+  <si>
+    <t>STAT</t>
+  </si>
+  <si>
+    <t>CNAPS</t>
+  </si>
+  <si>
+    <t>lkfskjfmf</t>
+  </si>
+  <si>
+    <t>tsisy</t>
   </si>
 </sst>
 </file>
@@ -143,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -166,16 +181,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -491,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431D5AF4-6942-4C44-8FEC-F31AB43C3EB5}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -519,7 +547,7 @@
     <col min="23" max="23" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,8 +617,17 @@
       <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="X1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -618,12 +655,25 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
+      <c r="T2" s="5">
+        <v>46205</v>
+      </c>
+      <c r="U2" s="5">
+        <v>41255</v>
+      </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
+      <c r="X2" s="3">
+        <v>1222222</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -647,8 +697,11 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -672,8 +725,11 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -697,6 +753,9 @@
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Template_insertion_adherents.xlsx
+++ b/Template_insertion_adherents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\sebtp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7801F72A-014A-4F27-9215-5A25AE307D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABCB9CA-FF5F-43A3-8F11-FFB58E246691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1992" windowWidth="17280" windowHeight="8880" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>email</t>
   </si>
@@ -45,9 +45,6 @@
     <t>activite</t>
   </si>
   <si>
-    <t>filiere</t>
-  </si>
-  <si>
     <t>nb_employes</t>
   </si>
   <si>
@@ -72,18 +69,12 @@
     <t>raison départ</t>
   </si>
   <si>
-    <t>statut demande</t>
-  </si>
-  <si>
     <t>validation bureau</t>
   </si>
   <si>
     <t>validation DG</t>
   </si>
   <si>
-    <t>type (ONG, entreprise, sponsor)</t>
-  </si>
-  <si>
     <t>fichiers</t>
   </si>
   <si>
@@ -93,21 +84,12 @@
     <t>cot_fmfp (Oui/Non)</t>
   </si>
   <si>
-    <t>statut membre (Simple/Bureau)</t>
-  </si>
-  <si>
-    <t>statut (radie, actif, inactif, demande)</t>
-  </si>
-  <si>
     <t>actif</t>
   </si>
   <si>
     <t>OTI</t>
   </si>
   <si>
-    <t>secoti@oti.mg</t>
-  </si>
-  <si>
     <t>NIF</t>
   </si>
   <si>
@@ -121,6 +103,84 @@
   </si>
   <si>
     <t>tsisy</t>
+  </si>
+  <si>
+    <t>ONG</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>bureau</t>
+  </si>
+  <si>
+    <t>statut membre (simple/bureau)</t>
+  </si>
+  <si>
+    <t>filiere (Fournisseur de biens et services, BTP / Construction, Bureau d'études)</t>
+  </si>
+  <si>
+    <t>statut demande (attente_bureau/attente_ag/adhere, rejete)</t>
+  </si>
+  <si>
+    <t>type (ong/entreprise/sponsor)</t>
+  </si>
+  <si>
+    <t>statut (radie/actif/inactif/demande)</t>
+  </si>
+  <si>
+    <t>comm.si@oti.mg</t>
+  </si>
+  <si>
+    <t>BTP</t>
+  </si>
+  <si>
+    <t>Nom RH</t>
+  </si>
+  <si>
+    <t>Num RH</t>
+  </si>
+  <si>
+    <t>Mail RH</t>
+  </si>
+  <si>
+    <t>Nom Fin</t>
+  </si>
+  <si>
+    <t>Num Fin</t>
+  </si>
+  <si>
+    <t>Mail Fin</t>
+  </si>
+  <si>
+    <t>Tsantaniony</t>
+  </si>
+  <si>
+    <t>tsanta.rakotoarimalala@oti.mg</t>
+  </si>
+  <si>
+    <t>Rina</t>
+  </si>
+  <si>
+    <t>rina@oti.mg</t>
+  </si>
+  <si>
+    <t>BTP / Construction, Bureau d'etudes</t>
+  </si>
+  <si>
+    <t>Referent SEBTP</t>
+  </si>
+  <si>
+    <t>Num ref</t>
+  </si>
+  <si>
+    <t>Mail ref</t>
+  </si>
+  <si>
+    <t>Mr ref</t>
+  </si>
+  <si>
+    <t>ref@test.com</t>
   </si>
 </sst>
 </file>
@@ -519,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431D5AF4-6942-4C44-8FEC-F31AB43C3EB5}">
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -528,7 +588,7 @@
     <col min="4" max="4" width="26.44140625" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="7" max="7" width="64.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.44140625" customWidth="1"/>
     <col min="9" max="9" width="20.44140625" customWidth="1"/>
     <col min="10" max="10" width="15.21875" customWidth="1"/>
@@ -540,14 +600,18 @@
     <col min="16" max="16" width="31" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.109375" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
-    <col min="19" max="19" width="18.109375" customWidth="1"/>
+    <col min="19" max="19" width="51.109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="21" customWidth="1"/>
     <col min="21" max="21" width="17.6640625" customWidth="1"/>
     <col min="22" max="22" width="37" customWidth="1"/>
     <col min="23" max="23" width="13.88671875" customWidth="1"/>
+    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,90 +631,125 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="Y1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="Z1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>29</v>
+      <c r="AA1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
@@ -661,19 +760,48 @@
       <c r="U2" s="5">
         <v>41255</v>
       </c>
-      <c r="V2" s="3"/>
+      <c r="V2" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3">
         <v>1222222</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>3800123456</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>380030696</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>380030994</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -700,8 +828,17 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -728,8 +865,17 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -756,11 +902,24 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{9A0FD041-1250-4C6A-9B1B-06B7A10EAE0D}"/>
+    <hyperlink ref="AF2" r:id="rId2" xr:uid="{F5816441-8416-406A-A6DD-76D1A70EA7E0}"/>
+    <hyperlink ref="AI2" r:id="rId3" xr:uid="{A9F4704E-B105-4988-881B-D88BE8E6FA96}"/>
+    <hyperlink ref="AC2" r:id="rId4" xr:uid="{D0BB8037-FC9A-491B-962F-B87E02C66E51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/Template_insertion_adherents.xlsx
+++ b/Template_insertion_adherents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\sebtp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABCB9CA-FF5F-43A3-8F11-FFB58E246691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35910C1-26D9-478E-A38E-050DE5439601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" xr2:uid="{7D5D9DA3-7695-4AB8-AE95-6DED58FAFFA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
   <si>
     <t>email</t>
   </si>
@@ -87,9 +87,6 @@
     <t>actif</t>
   </si>
   <si>
-    <t>OTI</t>
-  </si>
-  <si>
     <t>NIF</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>statut (radie/actif/inactif/demande)</t>
   </si>
   <si>
-    <t>comm.si@oti.mg</t>
-  </si>
-  <si>
     <t>BTP</t>
   </si>
   <si>
@@ -181,6 +175,54 @@
   </si>
   <si>
     <t>ref@test.com</t>
+  </si>
+  <si>
+    <t>Lot IVJ 163 Ambohimanarina</t>
+  </si>
+  <si>
+    <t>RAMIJOROA Lalaina Kiady Aaron</t>
+  </si>
+  <si>
+    <t>Président du SEBTP</t>
+  </si>
+  <si>
+    <t>aaronkiady77@gmail.com</t>
+  </si>
+  <si>
+    <t>ramijoroaaaron@gmail.com</t>
+  </si>
+  <si>
+    <t>AARON GROUP</t>
+  </si>
+  <si>
+    <t>BTP / Construction</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>simple</t>
+  </si>
+  <si>
+    <t>Tresorier du SEBTP</t>
+  </si>
+  <si>
+    <t>Bandy milay</t>
+  </si>
+  <si>
+    <t>entreprise</t>
+  </si>
+  <si>
+    <t>S65S3SFR53</t>
+  </si>
+  <si>
+    <t>REFCNAPS</t>
+  </si>
+  <si>
+    <t>ref@erent.com</t>
+  </si>
+  <si>
+    <t>KIADY</t>
   </si>
 </sst>
 </file>
@@ -583,7 +625,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
     <col min="4" max="4" width="26.44140625" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
@@ -605,6 +647,7 @@
     <col min="21" max="21" width="17.6640625" customWidth="1"/>
     <col min="22" max="22" width="37" customWidth="1"/>
     <col min="23" max="23" width="13.88671875" customWidth="1"/>
+    <col min="24" max="24" width="11" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="10" bestFit="1" customWidth="1"/>
@@ -631,7 +674,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -649,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>10</v>
@@ -658,7 +701,7 @@
         <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -667,7 +710,7 @@
         <v>13</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
@@ -676,77 +719,91 @@
         <v>15</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="X1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="AA1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AB1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="AD1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="B2" s="3">
+        <v>381053233</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="H2" s="3">
+        <v>20</v>
+      </c>
       <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="3">
+        <v>381053233</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="s">
         <v>19</v>
@@ -758,85 +815,147 @@
         <v>46205</v>
       </c>
       <c r="U2" s="5">
-        <v>41255</v>
+        <v>46215</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3">
         <v>1222222</v>
       </c>
       <c r="Y2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="AA2" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB2" s="3">
-        <v>3800123456</v>
+        <v>380012345</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE2" s="3">
         <v>380030696</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AH2" s="3">
         <v>380030994</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="A3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="3">
+        <v>380933982</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="3">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="3">
+        <v>381053233</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="P3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="T3" s="5">
+        <v>46223</v>
+      </c>
+      <c r="U3" s="5">
+        <v>46225</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
+      <c r="X3" s="3">
+        <v>2103206510</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>380030440</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>380030696</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>380030994</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -918,8 +1037,12 @@
     <hyperlink ref="AF2" r:id="rId2" xr:uid="{F5816441-8416-406A-A6DD-76D1A70EA7E0}"/>
     <hyperlink ref="AI2" r:id="rId3" xr:uid="{A9F4704E-B105-4988-881B-D88BE8E6FA96}"/>
     <hyperlink ref="AC2" r:id="rId4" xr:uid="{D0BB8037-FC9A-491B-962F-B87E02C66E51}"/>
+    <hyperlink ref="A3" r:id="rId5" xr:uid="{2D425FA1-F4A7-4758-AC2A-47ED6BE299F5}"/>
+    <hyperlink ref="AC3" r:id="rId6" xr:uid="{55D8BAFB-AC6D-4F9B-AF4E-02290733D685}"/>
+    <hyperlink ref="AF3" r:id="rId7" xr:uid="{17A7429A-9A0D-419E-A18E-27FFC752101C}"/>
+    <hyperlink ref="AI3" r:id="rId8" xr:uid="{3765F1F7-1A74-43DF-B4DE-A3F7EE07DD92}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>